--- a/templates/Base_Datos_Seguros_Vehiculares_FIAS.xlsx
+++ b/templates/Base_Datos_Seguros_Vehiculares_FIAS.xlsx
@@ -2,18 +2,18 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="00_Dashboard" sheetId="1" r:id="R9cb49d19083f4917"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="00_Instrucciones" sheetId="2" r:id="R4b9e3855a5e345a4"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="01_Polizas" sheetId="3" r:id="R65eb6f4fbac54316"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="02_Bienes_Asegurados" sheetId="4" r:id="R8b71204b9b284942"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="03_Coberturas" sheetId="5" r:id="R89d3f2e868974e2c"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="04_Asistencia" sheetId="6" r:id="Rad019d0188194a56"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="05_Procedimiento_Siniestro" sheetId="7" r:id="R520202bad09f47a2"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="06_Documentos_Requeridos" sheetId="8" r:id="R6dc67dd1379143bd"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="07_FAQ" sheetId="9" r:id="R6d422f4a3c204aff"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="08_Videos" sheetId="10" r:id="R2dab6970e8814c5f"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="09_Config_Web" sheetId="11" r:id="Rb1912556f87c4199"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="10_Catalogos" sheetId="12" r:id="R66a776ea4ece4c28"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="00_Dashboard" sheetId="1" r:id="R1cb205c866ef4445"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="00_Instrucciones" sheetId="2" r:id="Ra82b6a9e8be544f5"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="01_Polizas" sheetId="3" r:id="Rb018159814954983"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="02_Bienes_Asegurados" sheetId="4" r:id="R75275b3ac45d4102"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="03_Coberturas" sheetId="5" r:id="Ra61be798ae394216"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="04_Asistencia" sheetId="6" r:id="R0306965a3a6a4ef1"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="05_Procedimiento_Siniestro" sheetId="7" r:id="R21fe94093f634317"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="06_Documentos_Requeridos" sheetId="8" r:id="R6f64f558fd1e4681"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="07_FAQ" sheetId="9" r:id="Re6a156e00e9c4598"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="08_Videos" sheetId="10" r:id="R7abe762131b6436d"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="09_Config_Web" sheetId="11" r:id="Reb6a22c64d4746ef"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="10_Catalogos" sheetId="12" r:id="R492b47f9fdb141cd"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -52,7 +52,7 @@
       <x:name val="Carlito"/>
     </x:font>
   </x:fonts>
-  <x:fills count="5">
+  <x:fills count="6">
     <x:fill>
       <x:patternFill patternType="none"/>
     </x:fill>
@@ -74,6 +74,11 @@
         <x:fgColor rgb="FF0F6F49"/>
       </x:patternFill>
     </x:fill>
+    <x:fill>
+      <x:patternFill patternType="solid">
+        <x:fgColor rgb="FF0B8A55"/>
+      </x:patternFill>
+    </x:fill>
   </x:fills>
   <x:borders count="2">
     <x:border/>
@@ -82,7 +87,7 @@
   <x:cellStyleXfs count="1">
     <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </x:cellStyleXfs>
-  <x:cellXfs count="39">
+  <x:cellXfs count="40">
     <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <x:xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <x:xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
@@ -162,6 +167,9 @@
       <x:alignment wrapText="1"/>
     </x:xf>
     <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <x:xf numFmtId="0" fontId="3" fillId="5" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="center" vertical="center" wrapText="1"/>
+    </x:xf>
   </x:cellXfs>
   <x:cellStyles count="1">
     <x:cellStyle name="Normal" xfId="0"/>
@@ -722,7 +730,7 @@
   </x:dataValidations>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R366461fd9a1245c8"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R03f023c13c99433d"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -865,7 +873,7 @@
   </x:dataValidations>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R0e1ea9a0a1e24e8d"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rede5b04f6ba24624"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -1042,7 +1050,7 @@
   </x:dataValidations>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R0ad28e9d387d43e4"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rf5fd20d440c545c1"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -2134,7 +2142,7 @@
   </x:dataValidations>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R8f7eb7bd59cf4f40"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rd50f9647ab084329"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -3706,7 +3714,7 @@
   </x:dataValidations>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rbe1c53150e2845a2"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R2b8c6355c5cd4e26"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -3715,71 +3723,71 @@
 <x:worksheet xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheetFormatPr defaultRowHeight="15"/>
   <x:cols>
-    <x:col min="1" max="1" width="16" hidden="0" customWidth="1"/>
-    <x:col min="2" max="2" width="14" hidden="0" customWidth="1"/>
-    <x:col min="3" max="3" width="14" hidden="0" customWidth="1"/>
-    <x:col min="4" max="4" width="16" hidden="0" customWidth="1"/>
-    <x:col min="5" max="5" width="40" hidden="0" customWidth="1"/>
-    <x:col min="6" max="6" width="40" hidden="0" customWidth="1"/>
-    <x:col min="7" max="7" width="16" hidden="0" customWidth="1"/>
-    <x:col min="8" max="8" width="40" hidden="0" customWidth="1"/>
-    <x:col min="9" max="9" width="16" hidden="0" customWidth="1"/>
-    <x:col min="10" max="10" width="14" hidden="0" customWidth="1"/>
+    <x:col min="1" max="1" width="13" hidden="0" customWidth="1"/>
+    <x:col min="2" max="2" width="9.880000114440918" hidden="0" customWidth="1"/>
+    <x:col min="3" max="3" width="8.75" hidden="0" customWidth="1"/>
+    <x:col min="4" max="4" width="16.6299991607666" hidden="0" customWidth="1"/>
+    <x:col min="5" max="5" width="36" hidden="0" customWidth="1"/>
+    <x:col min="6" max="6" width="48" hidden="0" customWidth="1"/>
+    <x:col min="7" max="7" width="11" hidden="0" customWidth="1"/>
+    <x:col min="8" max="8" width="28" hidden="0" customWidth="1"/>
+    <x:col min="9" max="9" width="28" hidden="0" customWidth="1"/>
+    <x:col min="10" max="10" width="13.25" hidden="0" customWidth="1"/>
   </x:cols>
   <x:sheetData>
     <x:row r="1" ht="28" customHeight="1">
-      <x:c r="A1" s="29" t="str">
+      <x:c r="A1" s="39" t="str">
         <x:v>id_cobertura</x:v>
       </x:c>
-      <x:c r="B1" s="29" t="str">
+      <x:c r="B1" s="39" t="str">
         <x:v>id_poliza</x:v>
       </x:c>
-      <x:c r="C1" s="29" t="str">
+      <x:c r="C1" s="39" t="str">
         <x:v>id_bien</x:v>
       </x:c>
-      <x:c r="D1" s="29" t="str">
+      <x:c r="D1" s="39" t="str">
         <x:v>tipo_cobertura</x:v>
       </x:c>
-      <x:c r="E1" s="29" t="str">
+      <x:c r="E1" s="39" t="str">
         <x:v>nombre_cobertura</x:v>
       </x:c>
-      <x:c r="F1" s="29" t="str">
+      <x:c r="F1" s="39" t="str">
         <x:v>descripcion</x:v>
       </x:c>
-      <x:c r="G1" s="29" t="str">
+      <x:c r="G1" s="39" t="str">
         <x:v>limite_usd</x:v>
       </x:c>
-      <x:c r="H1" s="29" t="str">
+      <x:c r="H1" s="39" t="str">
         <x:v>deducible</x:v>
       </x:c>
-      <x:c r="I1" s="29" t="str">
+      <x:c r="I1" s="39" t="str">
         <x:v>aplica_a</x:v>
       </x:c>
-      <x:c r="J1" s="29" t="str">
+      <x:c r="J1" s="39" t="str">
         <x:v>mostrar_web</x:v>
       </x:c>
     </x:row>
     <x:row r="2">
       <x:c r="A2" s="32" t="str">
-        <x:v>COB-001</x:v>
+        <x:v>COB-DANOS-001</x:v>
       </x:c>
       <x:c r="B2" s="32" t="str"/>
       <x:c r="C2" s="32" t="str"/>
       <x:c r="D2" s="32" t="str">
-        <x:v>Todo riesgo</x:v>
+        <x:v>Daños propios</x:v>
       </x:c>
       <x:c r="E2" s="32" t="str">
-        <x:v>Pérdida total del vehículo por daños</x:v>
+        <x:v>Choque y volcadura</x:v>
       </x:c>
       <x:c r="F2" s="32" t="str">
-        <x:v>Cubre eventos de pérdida total por daños conforme condiciones particulares y generales de la póliza.</x:v>
+        <x:v>Cubre pérdida parcial o total del vehículo asegurado por choque o volcadura, conforme las condiciones de la póliza.</x:v>
       </x:c>
       <x:c r="G2" s="36" t="str"/>
       <x:c r="H2" s="32" t="str">
         <x:v>Según póliza</x:v>
       </x:c>
       <x:c r="I2" s="32" t="str">
-        <x:v>Todos</x:v>
+        <x:v>Vehículos y motos</x:v>
       </x:c>
       <x:c r="J2" s="32" t="str">
         <x:v>SI</x:v>
@@ -3787,25 +3795,25 @@
     </x:row>
     <x:row r="3">
       <x:c r="A3" s="32" t="str">
-        <x:v>COB-002</x:v>
+        <x:v>COB-DANOS-002</x:v>
       </x:c>
       <x:c r="B3" s="32" t="str"/>
       <x:c r="C3" s="32" t="str"/>
       <x:c r="D3" s="32" t="str">
-        <x:v>Todo riesgo</x:v>
+        <x:v>Daños propios</x:v>
       </x:c>
       <x:c r="E3" s="32" t="str">
-        <x:v>Pérdida parcial del vehículo por daños</x:v>
+        <x:v>Incendio, rayo, autoignición y explosión</x:v>
       </x:c>
       <x:c r="F3" s="32" t="str">
-        <x:v>Cubre daños parciales del vehículo asegurado, sujetos a deducibles y exclusiones contractuales.</x:v>
+        <x:v>Cubre daños ocasionados por fuego, rayo, autoignición o explosión cuando estén contemplados en la póliza.</x:v>
       </x:c>
       <x:c r="G3" s="36" t="str"/>
       <x:c r="H3" s="32" t="str">
         <x:v>Según póliza</x:v>
       </x:c>
       <x:c r="I3" s="32" t="str">
-        <x:v>Todos</x:v>
+        <x:v>Vehículos y motos</x:v>
       </x:c>
       <x:c r="J3" s="32" t="str">
         <x:v>SI</x:v>
@@ -3813,25 +3821,25 @@
     </x:row>
     <x:row r="4">
       <x:c r="A4" s="32" t="str">
-        <x:v>COB-003</x:v>
+        <x:v>COB-DANOS-003</x:v>
       </x:c>
       <x:c r="B4" s="32" t="str"/>
       <x:c r="C4" s="32" t="str"/>
       <x:c r="D4" s="32" t="str">
-        <x:v>Robo / hurto</x:v>
+        <x:v>Daños propios</x:v>
       </x:c>
       <x:c r="E4" s="32" t="str">
-        <x:v>Pérdida total o parcial por robo o hurto</x:v>
+        <x:v>Rotura de vidrios e impacto con objetos sólidos</x:v>
       </x:c>
       <x:c r="F4" s="32" t="str">
-        <x:v>Cubre pérdida por robo o hurto de acuerdo con los límites y requisitos de notificación establecidos.</x:v>
+        <x:v>Cubre la rotura de vidrios y daños por impacto con objetos sólidos, de acuerdo con los términos contratados.</x:v>
       </x:c>
       <x:c r="G4" s="36" t="str"/>
       <x:c r="H4" s="32" t="str">
         <x:v>Según póliza</x:v>
       </x:c>
       <x:c r="I4" s="32" t="str">
-        <x:v>Todos</x:v>
+        <x:v>Vehículos y motos</x:v>
       </x:c>
       <x:c r="J4" s="32" t="str">
         <x:v>SI</x:v>
@@ -3839,25 +3847,25 @@
     </x:row>
     <x:row r="5">
       <x:c r="A5" s="32" t="str">
-        <x:v>COB-004</x:v>
+        <x:v>COB-DANOS-004</x:v>
       </x:c>
       <x:c r="B5" s="32" t="str"/>
       <x:c r="C5" s="32" t="str"/>
       <x:c r="D5" s="32" t="str">
-        <x:v>Responsabilidad civil</x:v>
+        <x:v>Robo / hurto</x:v>
       </x:c>
       <x:c r="E5" s="32" t="str">
-        <x:v>Responsabilidad civil a terceros</x:v>
+        <x:v>Robo o hurto total y parcial</x:v>
       </x:c>
       <x:c r="F5" s="32" t="str">
-        <x:v>Límite único combinado según cada póliza o condiciones particulares.</x:v>
-      </x:c>
-      <x:c r="G5" s="36" t="str">
-        <x:v>30000</x:v>
-      </x:c>
-      <x:c r="H5" s="32" t="str"/>
+        <x:v>Cubre la pérdida total o parcial del vehículo o de partes aseguradas por robo o hurto, sujeto a denuncia, notificación y respaldos.</x:v>
+      </x:c>
+      <x:c r="G5" s="36" t="str"/>
+      <x:c r="H5" s="32" t="str">
+        <x:v>Según póliza</x:v>
+      </x:c>
       <x:c r="I5" s="32" t="str">
-        <x:v>Vehículos</x:v>
+        <x:v>Vehículos y motos</x:v>
       </x:c>
       <x:c r="J5" s="32" t="str">
         <x:v>SI</x:v>
@@ -3865,25 +3873,183 @@
     </x:row>
     <x:row r="6">
       <x:c r="A6" s="32" t="str">
-        <x:v>COB-005</x:v>
+        <x:v>COB-DANOS-005</x:v>
       </x:c>
       <x:c r="B6" s="32" t="str"/>
       <x:c r="C6" s="32" t="str"/>
       <x:c r="D6" s="32" t="str">
-        <x:v>Asistencia</x:v>
+        <x:v>Fenómenos naturales</x:v>
       </x:c>
       <x:c r="E6" s="32" t="str">
-        <x:v>Servicio de grúa, wincha y asistencia vial</x:v>
+        <x:v>Inundación, terremoto, erupción, deslizamiento y caída de rocas</x:v>
       </x:c>
       <x:c r="F6" s="32" t="str">
-        <x:v>Asistencia coordinada mediante los canales oficiales de la aseguradora y proveedor asignado.</x:v>
+        <x:v>Cubre eventos de la naturaleza que produzcan daños al bien asegurado, cuando consten en condiciones generales o particulares.</x:v>
       </x:c>
       <x:c r="G6" s="36" t="str"/>
-      <x:c r="H6" s="32" t="str"/>
+      <x:c r="H6" s="32" t="str">
+        <x:v>Según póliza</x:v>
+      </x:c>
       <x:c r="I6" s="32" t="str">
-        <x:v>Vehículos</x:v>
+        <x:v>Vehículos y motos</x:v>
       </x:c>
       <x:c r="J6" s="32" t="str">
+        <x:v>SI</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="7">
+      <x:c r="A7" s="32" t="str">
+        <x:v>COB-DANOS-006</x:v>
+      </x:c>
+      <x:c r="B7" s="32" t="str"/>
+      <x:c r="C7" s="32" t="str"/>
+      <x:c r="D7" s="32" t="str">
+        <x:v>Impactos y caídas</x:v>
+      </x:c>
+      <x:c r="E7" s="32" t="str">
+        <x:v>Caída de árboles, edificios, aeronaves o partes de ellos</x:v>
+      </x:c>
+      <x:c r="F7" s="32" t="str">
+        <x:v>Cubre daños causados por caída de objetos externos sobre el vehículo asegurado, conforme condiciones de la póliza.</x:v>
+      </x:c>
+      <x:c r="G7" s="36" t="str"/>
+      <x:c r="H7" s="32" t="str">
+        <x:v>Según póliza</x:v>
+      </x:c>
+      <x:c r="I7" s="32" t="str">
+        <x:v>Vehículos y motos</x:v>
+      </x:c>
+      <x:c r="J7" s="32" t="str">
+        <x:v>SI</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="8">
+      <x:c r="A8" s="32" t="str">
+        <x:v>COB-DANOS-007</x:v>
+      </x:c>
+      <x:c r="B8" s="32" t="str"/>
+      <x:c r="C8" s="32" t="str"/>
+      <x:c r="D8" s="32" t="str">
+        <x:v>Orden público</x:v>
+      </x:c>
+      <x:c r="E8" s="32" t="str">
+        <x:v>Motín, huelga, conmoción civil y daños maliciosos</x:v>
+      </x:c>
+      <x:c r="F8" s="32" t="str">
+        <x:v>Cubre eventos especiales relacionados con orden público, sujetos a las condiciones y exclusiones de la póliza.</x:v>
+      </x:c>
+      <x:c r="G8" s="36" t="str"/>
+      <x:c r="H8" s="32" t="str">
+        <x:v>Según póliza</x:v>
+      </x:c>
+      <x:c r="I8" s="32" t="str">
+        <x:v>Vehículos y motos</x:v>
+      </x:c>
+      <x:c r="J8" s="32" t="str">
+        <x:v>SI</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="9">
+      <x:c r="A9" s="32" t="str">
+        <x:v>COB-DANOS-008</x:v>
+      </x:c>
+      <x:c r="B9" s="32" t="str"/>
+      <x:c r="C9" s="32" t="str"/>
+      <x:c r="D9" s="32" t="str">
+        <x:v>Tránsito y operación</x:v>
+      </x:c>
+      <x:c r="E9" s="32" t="str">
+        <x:v>Paso de puentes y gabarras; tránsito por caminos no entregados al uso público</x:v>
+      </x:c>
+      <x:c r="F9" s="32" t="str">
+        <x:v>Cubre determinados eventos durante la circulación por rutas o pasos descritos en la póliza, siempre que sean aplicables.</x:v>
+      </x:c>
+      <x:c r="G9" s="36" t="str"/>
+      <x:c r="H9" s="32" t="str">
+        <x:v>Según póliza</x:v>
+      </x:c>
+      <x:c r="I9" s="32" t="str">
+        <x:v>Vehículos y motos</x:v>
+      </x:c>
+      <x:c r="J9" s="32" t="str">
+        <x:v>SI</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="10">
+      <x:c r="A10" s="32" t="str">
+        <x:v>COB-DANOS-009</x:v>
+      </x:c>
+      <x:c r="B10" s="32" t="str"/>
+      <x:c r="C10" s="32" t="str"/>
+      <x:c r="D10" s="32" t="str">
+        <x:v>Responsabilidad civil</x:v>
+      </x:c>
+      <x:c r="E10" s="32" t="str">
+        <x:v>Responsabilidad civil a terceros</x:v>
+      </x:c>
+      <x:c r="F10" s="32" t="str">
+        <x:v>Amparo frente a daños a terceros hasta el límite establecido en cada póliza o condiciones particulares.</x:v>
+      </x:c>
+      <x:c r="G10" s="36" t="str">
+        <x:v>30000</x:v>
+      </x:c>
+      <x:c r="H10" s="32" t="str">
+        <x:v>Según póliza</x:v>
+      </x:c>
+      <x:c r="I10" s="32" t="str">
+        <x:v>Principalmente vehículos; motos según póliza</x:v>
+      </x:c>
+      <x:c r="J10" s="32" t="str">
+        <x:v>SI</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="11">
+      <x:c r="A11" s="32" t="str">
+        <x:v>COB-DANOS-010</x:v>
+      </x:c>
+      <x:c r="B11" s="32" t="str"/>
+      <x:c r="C11" s="32" t="str"/>
+      <x:c r="D11" s="32" t="str">
+        <x:v>Amparos personales</x:v>
+      </x:c>
+      <x:c r="E11" s="32" t="str">
+        <x:v>Muerte accidental, invalidez y gastos médicos por ocupante</x:v>
+      </x:c>
+      <x:c r="F11" s="32" t="str">
+        <x:v>Amparos personales sujetos al límite por ocupante, número de ocupantes y condiciones particulares de cada póliza.</x:v>
+      </x:c>
+      <x:c r="G11" s="36" t="str"/>
+      <x:c r="H11" s="32" t="str">
+        <x:v>Según póliza</x:v>
+      </x:c>
+      <x:c r="I11" s="32" t="str">
+        <x:v>Según póliza</x:v>
+      </x:c>
+      <x:c r="J11" s="32" t="str">
+        <x:v>SI</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="12">
+      <x:c r="A12" s="32" t="str">
+        <x:v>COB-DANOS-011</x:v>
+      </x:c>
+      <x:c r="B12" s="32" t="str"/>
+      <x:c r="C12" s="32" t="str"/>
+      <x:c r="D12" s="32" t="str">
+        <x:v>Asistencia vial</x:v>
+      </x:c>
+      <x:c r="E12" s="32" t="str">
+        <x:v>Grúa, wincha, auxilio vial y asistencia en siniestro</x:v>
+      </x:c>
+      <x:c r="F12" s="32" t="str">
+        <x:v>Servicio coordinado por canales oficiales del broker, aseguradora o proveedor asignado. No se recomienda contratar proveedores externos sin autorización.</x:v>
+      </x:c>
+      <x:c r="G12" s="36" t="str"/>
+      <x:c r="H12" s="32" t="str"/>
+      <x:c r="I12" s="32" t="str">
+        <x:v>Según póliza</x:v>
+      </x:c>
+      <x:c r="J12" s="32" t="str">
         <x:v>SI</x:v>
       </x:c>
     </x:row>
@@ -3895,7 +4061,7 @@
   </x:dataValidations>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rf0326d4759ba4d1d"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R7afd9800ed3c4198"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -4018,7 +4184,7 @@
   </x:dataValidations>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rda3cf0b8b7ee4924"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rdf4744aead354fcf"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -4230,7 +4396,7 @@
   </x:dataValidations>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R38aa16f9b0f64bfe"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R8aedbe2bfb7c4a02"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -4417,7 +4583,7 @@
   </x:dataValidations>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rb5bb1a8d1bde4042"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R0af43a5a9ee04dd2"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -4545,7 +4711,7 @@
   </x:dataValidations>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R2fc146385d334a56"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R9896ba1d7e8e4742"/>
   </x:tableParts>
 </x:worksheet>
 </file>